--- a/文件/程式碼截圖/截取完成文字檔/推薦4/推薦參數.xlsx
+++ b/文件/程式碼截圖/截取完成文字檔/推薦4/推薦參數.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/36338b096113435e/桌面/專題/goodbye/文件/程式碼截圖/截取完成文字檔/推薦4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="11_AD4DBB64A54DDB1B405E387065DB25EF4F90DF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1D27BE4-DF17-412F-8235-7FE342D76D49}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="11_AD4DBB64A54DDB1B405E387065DB25EF4F90DF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{089B7472-B7A7-412E-BDF7-007211E81CE9}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="75" yWindow="1485" windowWidth="14175" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="shop" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="101">
   <si>
     <t>參數</t>
   </si>
@@ -198,13 +198,7 @@
     <t>標籤匹配</t>
   </si>
   <si>
-    <t>title</t>
-  </si>
-  <si>
     <t>標題匹配</t>
-  </si>
-  <si>
-    <t>post_text</t>
   </si>
   <si>
     <t>內文匹配</t>
@@ -356,6 +350,14 @@
   </si>
   <si>
     <t>個人化：需要登入的 request；若未登入回傳空集合；personalized_*_recommendation(request: HttpRequest)</t>
+  </si>
+  <si>
+    <t>post_text</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>title</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -492,17 +494,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -519,10 +521,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -788,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.5703125" customWidth="1"/>
@@ -797,11 +795,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="50.25" x14ac:dyDescent="0.75">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
@@ -1110,13 +1108,73 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B40">
         <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="30" x14ac:dyDescent="0.45">
+      <c r="A46" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>31</v>
+      </c>
+      <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49">
+        <v>14</v>
+      </c>
+      <c r="C49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50">
+        <v>3</v>
+      </c>
+      <c r="C50" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51">
+        <v>7</v>
+      </c>
+      <c r="C51" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214BECB1-9E62-4452-9C4F-4472B63ED48D}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1139,11 +1197,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="50.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
@@ -1288,24 +1346,24 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="B25">
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.45">
@@ -1348,35 +1406,62 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B33">
         <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B34">
         <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B35">
         <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="30" x14ac:dyDescent="0.45">
+      <c r="A40" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42">
+        <v>14</v>
+      </c>
+      <c r="C42" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1393,166 +1478,166 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="63.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="14.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C2" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="B4" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="B5" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="9">
+        <v>20</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="11">
-        <v>20</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="11">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
